--- a/Data/Excel/npc_drop.xlsx
+++ b/Data/Excel/npc_drop.xlsx
@@ -161,13 +161,13 @@
     </row>
     <row r="5">
       <c r="B5">
-        <v>100101</v>
+        <v>30930001</v>
       </c>
       <c r="C5">
-        <v>1001</v>
+        <v>41000001</v>
       </c>
       <c r="D5">
-        <v>3000201</v>
+        <v>20500001</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -181,13 +181,13 @@
     </row>
     <row r="6">
       <c r="B6">
-        <v>100201</v>
+        <v>30930002</v>
       </c>
       <c r="C6">
-        <v>1002</v>
+        <v>41000002</v>
       </c>
       <c r="D6">
-        <v>1000101</v>
+        <v>20400001</v>
       </c>
       <c r="E6">
         <v>1</v>
